--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.24.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -601,16 +601,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: right to redeem â€” a question on which there is he</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: right to redeemâ€”a question on which there is here some</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]17</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]17</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L26: isolated marker/symbol line :: 17</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]17</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -654,22 +658,26 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+5206 CJK UNIFIED IDEOGRAPH-5206, U+7EBF CJK UNIFIED IDEOGRAPH-7EBF :: 分 线</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: =</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+4EA7 CJK UNIFIED IDEOGRAPH-4EA7 | isolated marker/symbol line :: 产</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: Â°</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -708,19 +716,19 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 3</t>
+          <t>L34: isolated marker/symbol line :: =</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L43: isolated marker/symbol line :: °</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -742,7 +750,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -759,19 +767,19 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: '</t>
+          <t>L35: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -810,19 +818,19 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 0</t>
+          <t>L36: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -861,19 +869,19 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 0</t>
+          <t>L37: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: "</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -912,19 +920,19 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 0-</t>
+          <t>L38: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: (</t>
+          <t>L86: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -966,12 +974,12 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 1</t>
+          <t>L40: isolated marker/symbol line :: 0-</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L88: isolated marker/symbol line :: (</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -993,7 +1001,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1013,12 +1021,12 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: B</t>
+          <t>L41: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L92: symbol-only separator/garbage line :: 0653</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1045,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1060,12 +1068,12 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 5</t>
+          <t>L42: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: r$</t>
+          <t>L92: symbol-only separator/garbage line :: 0653</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1087,12 +1095,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1107,12 +1115,12 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: B</t>
+          <t>L43: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 1</t>
+          <t>L95: isolated marker/symbol line :: r$</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1152,10 +1160,14 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L50: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 1</t>
+          <t>L97: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1198,7 +1210,7 @@
       <c r="N14" s="1" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 0</t>
+          <t>L99: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1241,7 +1253,7 @@
       <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L101: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1284,7 +1296,7 @@
       <c r="N16" s="1" t="inlineStr"/>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: B</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1325,7 +1337,11 @@
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
-      <c r="O17" s="1" t="inlineStr"/>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>L105: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
       <c r="R17" s="1" t="inlineStr"/>
